--- a/data/북원_홈페이지_프로그램관리.xlsx
+++ b/data/북원_홈페이지_프로그램관리.xlsx
@@ -1030,7 +1030,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>• 사진(선택): 이미지 주소(URL) 또는 photos/파일명.jpg. 비우면 주황 배경. 크기는 자동 조절(리사이즈 불필요).</t>
         </is>
@@ -1084,82 +1084,82 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" s="34">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>게시</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="46" t="inlineStr">
         <is>
           <t>프로그램명</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="46" t="inlineStr">
         <is>
           <t>강사</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="46" t="inlineStr">
         <is>
           <t>요일</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="46" t="inlineStr">
         <is>
           <t>시작시간</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="46" t="inlineStr">
         <is>
           <t>종료시간</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="46" t="inlineStr">
         <is>
           <t>장소</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="46" t="inlineStr">
         <is>
           <t>정원</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="46" t="inlineStr">
         <is>
           <t>수강료</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="46" t="inlineStr">
         <is>
           <t>재료비</t>
         </is>
       </c>
-      <c r="M4" s="45" t="inlineStr">
+      <c r="M4" s="46" t="inlineStr">
         <is>
           <t>운영시작</t>
         </is>
       </c>
-      <c r="N4" s="45" t="inlineStr">
+      <c r="N4" s="46" t="inlineStr">
         <is>
           <t>운영종료</t>
         </is>
       </c>
-      <c r="O4" s="45" t="inlineStr">
+      <c r="O4" s="46" t="inlineStr">
         <is>
           <t>안내문구</t>
         </is>
       </c>
-      <c r="P4" s="45" t="inlineStr">
+      <c r="P4" s="46" t="inlineStr">
         <is>
           <t>비고(홈페이지에 안 나옴)</t>
         </is>
@@ -1233,8 +1233,8 @@
       <c r="N5" s="52" t="n">
         <v>46356</v>
       </c>
-      <c r="O5" s="53" t="n"/>
-      <c r="P5" s="53" t="n"/>
+      <c r="O5" s="54" t="n"/>
+      <c r="P5" s="54" t="n"/>
       <c r="Q5" s="54" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="34">
@@ -1300,8 +1300,8 @@
       <c r="N6" s="52" t="n">
         <v>46356</v>
       </c>
-      <c r="O6" s="53" t="n"/>
-      <c r="P6" s="53" t="n"/>
+      <c r="O6" s="54" t="n"/>
+      <c r="P6" s="54" t="n"/>
       <c r="Q6" s="54" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="34">
@@ -4596,14 +4596,14 @@
     <row r="1" ht="20.1" customHeight="1" s="34">
       <c r="A1" s="43" t="inlineStr">
         <is>
-          <t>자세한 안내  ·  '자세한 안내 보기'를 눌렀을 때 펼쳐지는 내용</t>
+          <t>문의사항  ·  프로그램 화면 [문의사항] 버튼과 '자주 묻는 질문 › 프로그램'에 함께 나오는 내용</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="34">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>순서대로 나옵니다. 필요 없으면 게시를 X 로 두거나 행을 비우세요.</t>
+          <t>순서대로 나옵니다. 제목은 질문 형태로 써 주세요. 필요 없으면 게시를 X 로 두거나 행을 비우세요.</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="B5" s="66" t="inlineStr">
         <is>
-          <t>수강료와 재료비</t>
+          <t>수강료와 재료비는 얼마인가요?</t>
         </is>
       </c>
       <c r="C5" s="67" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="B6" s="66" t="inlineStr">
         <is>
-          <t>수강료를 내지 않아도 되는 분</t>
+          <t>수강료를 면제받을 수 있나요?</t>
         </is>
       </c>
       <c r="C6" s="67" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B7" s="66" t="inlineStr">
         <is>
-          <t>출석은 이렇게 합니다</t>
+          <t>출석은 어떻게 하나요?</t>
         </is>
       </c>
       <c r="C7" s="67" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="B8" s="66" t="inlineStr">
         <is>
-          <t>환불</t>
+          <t>수강료 환불은 어떻게 하나요?</t>
         </is>
       </c>
       <c r="C8" s="67" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="B9" s="66" t="inlineStr">
         <is>
-          <t>알아두실 점</t>
+          <t>수강할 때 알아두어야 할 점이 있나요?</t>
         </is>
       </c>
       <c r="C9" s="68" t="inlineStr">

--- a/data/북원_홈페이지_프로그램관리.xlsx
+++ b/data/북원_홈페이지_프로그램관리.xlsx
@@ -263,7 +263,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -468,6 +468,15 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4286,7 +4295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="33" min="1" max="1"/>
@@ -4567,6 +4576,66 @@
         </is>
       </c>
       <c r="C21" s="61" t="n"/>
+    </row>
+    <row r="22" ht="63" customHeight="1" s="34">
+      <c r="A22" s="69" t="inlineStr">
+        <is>
+          <t>이용절차</t>
+        </is>
+      </c>
+      <c r="B22" s="70" t="inlineStr">
+        <is>
+          <t>복지관 회원 가입
+수강 신청(방문)
+선정 여부 확인
+프로그램 참여</t>
+        </is>
+      </c>
+      <c r="C22" s="71" t="inlineStr">
+        <is>
+          <t>화면의 이용 절차 단계 · 한 줄에 한 단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="34">
+      <c r="A23" s="69" t="inlineStr">
+        <is>
+          <t>수강료안내</t>
+        </is>
+      </c>
+      <c r="B23" s="70" t="inlineStr">
+        <is>
+          <t>수강료 무료(일부 유료) · 교재비·재료비는 별도(본인 부담)</t>
+        </is>
+      </c>
+      <c r="C23" s="71" t="inlineStr">
+        <is>
+          <t>화면의 수강료 안내 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="108" customHeight="1" s="34">
+      <c r="A24" s="69" t="inlineStr">
+        <is>
+          <t>유의사항</t>
+        </is>
+      </c>
+      <c r="B24" s="70" t="inlineStr">
+        <is>
+          <t>수강 신청 시 회원증을 반드시 지참하세요.
+1인당 최대 3과목까지 신청할 수 있습니다.
+신청자가 정원을 넘으면 추첨으로 선정하며, 미선정자는 대기번호가 부여되어 잔여석 발생 시 순번대로 안내합니다.
+정원이 미달된 프로그램은 과목 수 제한 없이 추가 신청할 수 있습니다.
+3회 이상 무단결석 시 유선 연락 후 수강이 취소됩니다(연락이 되지 않아도 동일 적용).
+수강 신청 인원이 정원의 60% 미만이면 부득이하게 폐강될 수 있습니다.
+법정공휴일에는 프로그램이 휴강됩니다.</t>
+        </is>
+      </c>
+      <c r="C24" s="71" t="inlineStr">
+        <is>
+          <t>화면의 유의사항 · 한 줄에 한 항목 (셀 안 줄바꿈 Alt+Enter)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
